--- a/StatisticalAnalyses/Raji/output/SurvivalTable_CD70_Raji_Primary.xlsx
+++ b/StatisticalAnalyses/Raji/output/SurvivalTable_CD70_Raji_Primary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,10 +397,8 @@
           <t>Ctrl</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C2">
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -429,10 +427,8 @@
           <t>Ctrl</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C3">
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -461,10 +457,8 @@
           <t>CD70</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C4">
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -473,7 +467,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD70 nanoCAR-WT - 2 000 000</t>
+          <t>CD70 nanoCAR-WT - 4 000 000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -493,10 +487,8 @@
           <t>CD70</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C5">
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -505,7 +497,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD70 nanoCAR-KO - 2 000 000</t>
+          <t>CD70 nanoCAR-KO - 4 000 000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -517,39 +509,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E51</t>
+          <t>E62</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CD70</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MGAT5WT</t>
+          <t>Ctrl</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD70 nanoCAR-WT - 4 000 000</t>
+          <t>NTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100% (5/5)</t>
+          <t>100% (4/4)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E51</t>
+          <t>E62</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -557,24 +547,22 @@
           <t>CD70</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C7">
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MGAT5KO</t>
+          <t>MGAT5WT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD70 nanoCAR-KO - 4 000 000</t>
+          <t>CD70 nanoCAR-WT - 4 000 000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100% (5/5)</t>
+          <t>25% (1/4)</t>
         </is>
       </c>
     </row>
@@ -586,66 +574,62 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>CD70</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ctrl</t>
+          <t>MGAT5KO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NTC</t>
+          <t>CD70 nanoCAR-KO - 4 000 000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100% (4/4)</t>
+          <t>0% (0/4)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E62</t>
+          <t>E68</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CD70</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MGAT5WT</t>
+          <t>Ctrl</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD70 nanoCAR-WT - 4 000 000</t>
+          <t>NTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25% (1/4)</t>
+          <t>100% (5/5)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E62</t>
+          <t>E68</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -653,24 +637,22 @@
           <t>CD70</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C10">
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MGAT5KO</t>
+          <t>MGAT5WT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD70 nanoCAR-KO - 4 000 000</t>
+          <t>CD70 nanoCAR-WT - 4 000 000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0% (0/4)</t>
+          <t>80% (4/5)</t>
         </is>
       </c>
     </row>
@@ -682,66 +664,62 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>CD70</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ctrl</t>
+          <t>MGAT5KO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NTC</t>
+          <t>CD70 nanoCAR-KO - 4 000 000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100% (5/5)</t>
+          <t>0% (0/4)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E68</t>
+          <t>E74</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CD70</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MGAT5WT</t>
+          <t>Ctrl</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD70 nanoCAR-WT - 4 000 000</t>
+          <t>NTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80% (4/5)</t>
+          <t>100% (7/7)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E68</t>
+          <t>E74</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -749,24 +727,22 @@
           <t>CD70</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C13">
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MGAT5KO</t>
+          <t>MGAT5WT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD70 nanoCAR-KO - 4 000 000</t>
+          <t>CD70 nanoCAR-WT - 4 000 000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0% (0/4)</t>
+          <t>87.5% (7/8)</t>
         </is>
       </c>
     </row>
@@ -778,89 +754,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>CD70</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ctrl</t>
+          <t>MGAT5KO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NTC</t>
+          <t>CD70 nanoCAR-KO - 4 000 000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>100% (7/7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>E74</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CD70</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>MGAT5WT</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CD70 nanoCAR-WT - 4 000 000</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>87.5% (7/8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>E74</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CD70</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MGAT5KO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CD70 nanoCAR-KO - 4 000 000</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>33.3% (2/6)</t>
         </is>
